--- a/DXLibProject_Start/Resource/CSV/ItemRecipe.xlsx
+++ b/DXLibProject_Start/Resource/CSV/ItemRecipe.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Resource\CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Desktop\2nd_3DAction\DXLibProject_Start\Resource\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7302C936-5091-46EF-AD94-0C2C9027DC3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63374435-4624-46E8-89EF-926384387769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4050" windowWidth="21600" windowHeight="11295" xr2:uid="{218ED3FD-F1A3-4748-B667-4E69C2DB56C8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{218ED3FD-F1A3-4748-B667-4E69C2DB56C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="reference" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,20 +30,45 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="7">
+  <si>
+    <t>Invalid</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>Apple</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Beer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Bread</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cheese</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CheeseBread</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,21 +84,61 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -81,8 +147,20 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -103,9 +181,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -143,7 +221,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -249,7 +327,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -391,7 +469,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -399,11 +477,305 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FD5539C-A02E-4A9C-A317-3FB1655D1A37}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <dimension ref="A1:N6"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="13.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="str">
+        <f>reference!B2</f>
+        <v>Apple</v>
+      </c>
+      <c r="D1" s="1"/>
+      <c r="E1" s="2" t="str">
+        <f>reference!B3</f>
+        <v>Beer</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="2" t="str">
+        <f>reference!B4</f>
+        <v>Bread</v>
+      </c>
+      <c r="J1" s="1"/>
+      <c r="K1" s="2" t="str">
+        <f>reference!B5</f>
+        <v>Cheese</v>
+      </c>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2" t="str">
+        <f>reference!B6</f>
+        <v>CheeseBread</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="3" t="str">
+        <f>reference!B2</f>
+        <v>Apple</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="str">
+        <f>reference!B2</f>
+        <v>Apple</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="str">
+        <f>reference!B2</f>
+        <v>Apple</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="3" t="str">
+        <f>reference!B2</f>
+        <v>Apple</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3" t="str">
+        <f>reference!B2</f>
+        <v>Apple</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3" t="str">
+        <f>reference!B3</f>
+        <v>Beer</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="str">
+        <f>reference!B3</f>
+        <v>Beer</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="str">
+        <f>reference!B3</f>
+        <v>Beer</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="str">
+        <f>reference!B3</f>
+        <v>Beer</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="3" t="str">
+        <f>reference!B3</f>
+        <v>Beer</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="3" t="str">
+        <f>reference!B4</f>
+        <v>Bread</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="str">
+        <f>reference!B4</f>
+        <v>Bread</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="str">
+        <f>reference!B4</f>
+        <v>Bread</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3" t="str">
+        <f>reference!B4</f>
+        <v>Bread</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3" t="str">
+        <f>reference!B4</f>
+        <v>Bread</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3" t="str">
+        <f>reference!B5</f>
+        <v>Cheese</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="str">
+        <f>reference!B5</f>
+        <v>Cheese</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="str">
+        <f>reference!B5</f>
+        <v>Cheese</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="str">
+        <f>reference!B5</f>
+        <v>Cheese</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3" t="str">
+        <f>reference!B5</f>
+        <v>Cheese</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3" t="str">
+        <f>reference!B6</f>
+        <v>CheeseBread</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3" t="str">
+        <f>reference!B6</f>
+        <v>CheeseBread</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="str">
+        <f>reference!B6</f>
+        <v>CheeseBread</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="str">
+        <f>reference!B6</f>
+        <v>CheeseBread</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3" t="str">
+        <f>reference!B6</f>
+        <v>CheeseBread</v>
+      </c>
+      <c r="N6" s="4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5FB6F71D-1733-4E7C-A265-8B429449DFA9}">
+          <x14:formula1>
+            <xm:f>reference!$B:$B</xm:f>
+          </x14:formula1>
+          <xm:sqref>K1 B1 A2:B6 G2:H6 M2:N6 E1 D2:E6 H1 J2:K6 N1</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70688D63-630F-42E1-933D-89BA8B150096}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1">
+        <v>-1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/DXLibProject_Start/Resource/CSV/ItemRecipe.xlsx
+++ b/DXLibProject_Start/Resource/CSV/ItemRecipe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC_User\Desktop\2nd_3DAction\DXLibProject_Start\Resource\CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Resource\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63374435-4624-46E8-89EF-926384387769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF29484-9EA0-4AC5-8761-07065F47910D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{218ED3FD-F1A3-4748-B667-4E69C2DB56C8}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{218ED3FD-F1A3-4748-B667-4E69C2DB56C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,12 +30,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="9">
   <si>
     <t>Invalid</t>
     <phoneticPr fontId="1"/>
@@ -62,13 +65,19 @@
   <si>
     <t>CheeseBread</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Beer</t>
+  </si>
+  <si>
+    <t>Bread</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -181,9 +190,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -221,7 +230,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -327,7 +336,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -469,7 +478,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -478,7 +487,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FD5539C-A02E-4A9C-A317-3FB1655D1A37}">
   <dimension ref="A1:N6"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
@@ -487,7 +496,7 @@
     <col min="13" max="14" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="str">
         <f>reference!B2</f>
@@ -514,7 +523,7 @@
         <v>CheeseBread</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="str">
         <f>reference!B2</f>
         <v>Apple</v>
@@ -534,7 +543,7 @@
         <v>Apple</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3" t="str">
         <f>reference!B2</f>
@@ -548,10 +557,10 @@
         <v>Apple</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="str">
         <f>reference!B3</f>
         <v>Beer</v>
@@ -571,7 +580,7 @@
         <v>Beer</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J3" s="3" t="str">
         <f>reference!B3</f>
@@ -585,10 +594,10 @@
         <v>Beer</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="str">
         <f>reference!B4</f>
         <v>Bread</v>
@@ -608,7 +617,7 @@
         <v>Bread</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J4" s="3" t="str">
         <f>reference!B4</f>
@@ -622,10 +631,10 @@
         <v>Bread</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="str">
         <f>reference!B5</f>
         <v>Cheese</v>
@@ -645,7 +654,7 @@
         <v>Cheese</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J5" s="3" t="str">
         <f>reference!B5</f>
@@ -659,10 +668,10 @@
         <v>Cheese</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="str">
         <f>reference!B6</f>
         <v>CheeseBread</v>
@@ -682,7 +691,7 @@
         <v>CheeseBread</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J6" s="3" t="str">
         <f>reference!B6</f>
@@ -696,7 +705,7 @@
         <v>CheeseBread</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +719,7 @@
           <x14:formula1>
             <xm:f>reference!$B:$B</xm:f>
           </x14:formula1>
-          <xm:sqref>K1 B1 A2:B6 G2:H6 M2:N6 E1 D2:E6 H1 J2:K6 N1</xm:sqref>
+          <xm:sqref>K1 B1 A2:B6 M2:N6 N1 E1 D2:E6 H1 J2:K6 G2:H6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -721,12 +730,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70688D63-630F-42E1-933D-89BA8B150096}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1">
         <v>-1</v>
       </c>
@@ -734,7 +743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -742,7 +751,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -750,7 +759,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -758,7 +767,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -766,7 +775,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>

--- a/DXLibProject_Start/Resource/CSV/ItemRecipe.xlsx
+++ b/DXLibProject_Start/Resource/CSV/ItemRecipe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Resource\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF29484-9EA0-4AC5-8761-07065F47910D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE521B2-6E91-4E89-825E-19DB9080D46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{218ED3FD-F1A3-4748-B667-4E69C2DB56C8}"/>
+    <workbookView xWindow="675" yWindow="-15420" windowWidth="21600" windowHeight="11295" xr2:uid="{218ED3FD-F1A3-4748-B667-4E69C2DB56C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="11">
   <si>
     <t>Invalid</t>
     <phoneticPr fontId="1"/>
@@ -71,6 +71,12 @@
   </si>
   <si>
     <t>Bread</t>
+  </si>
+  <si>
+    <t>CheeseBread</t>
+  </si>
+  <si>
+    <t>Cheese</t>
   </si>
 </sst>
 </file>
@@ -489,10 +495,10 @@
   <dimension ref="A1:N6"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.125" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -529,7 +535,7 @@
         <v>Apple</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="str">
         <f>reference!B2</f>
@@ -550,14 +556,14 @@
         <v>Apple</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M2" s="3" t="str">
         <f>reference!B2</f>
         <v>Apple</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
@@ -566,7 +572,7 @@
         <v>Beer</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3" t="str">
         <f>reference!B3</f>
@@ -587,14 +593,14 @@
         <v>Beer</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M3" s="3" t="str">
         <f>reference!B3</f>
         <v>Beer</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
@@ -603,7 +609,7 @@
         <v>Bread</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="str">
         <f>reference!B4</f>
@@ -624,14 +630,14 @@
         <v>Bread</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M4" s="3" t="str">
         <f>reference!B4</f>
         <v>Bread</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
@@ -640,7 +646,7 @@
         <v>Cheese</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5" s="3" t="str">
         <f>reference!B5</f>
@@ -661,14 +667,14 @@
         <v>Cheese</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M5" s="3" t="str">
         <f>reference!B5</f>
         <v>Cheese</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
@@ -677,7 +683,7 @@
         <v>CheeseBread</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="str">
         <f>reference!B6</f>
@@ -698,14 +704,14 @@
         <v>CheeseBread</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="M6" s="3" t="str">
         <f>reference!B6</f>
         <v>CheeseBread</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +725,7 @@
           <x14:formula1>
             <xm:f>reference!$B:$B</xm:f>
           </x14:formula1>
-          <xm:sqref>K1 B1 A2:B6 M2:N6 N1 E1 D2:E6 H1 J2:K6 G2:H6</xm:sqref>
+          <xm:sqref>K1 B1 A2:B6 G2:H6 N1 E1 D2:E6 H1 J2:K6 M2:N6</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/DXLibProject_Start/Resource/CSV/ItemRecipe.xlsx
+++ b/DXLibProject_Start/Resource/CSV/ItemRecipe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Resource\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE521B2-6E91-4E89-825E-19DB9080D46A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2ED9B8-7778-471E-878D-18494FBE5D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="-15420" windowWidth="21600" windowHeight="11295" xr2:uid="{218ED3FD-F1A3-4748-B667-4E69C2DB56C8}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{218ED3FD-F1A3-4748-B667-4E69C2DB56C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
   <si>
     <t>Invalid</t>
     <phoneticPr fontId="1"/>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t>Cheese</t>
+  </si>
+  <si>
+    <t>Invalid</t>
   </si>
 </sst>
 </file>
@@ -535,35 +538,39 @@
         <v>Apple</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D2" s="3" t="str">
         <f>reference!B2</f>
         <v>Apple</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>1</v>
+      <c r="E2" s="4" t="str">
+        <f>B3</f>
+        <v>Invalid</v>
       </c>
       <c r="G2" s="3" t="str">
         <f>reference!B2</f>
         <v>Apple</v>
       </c>
-      <c r="H2" s="4" t="s">
-        <v>8</v>
+      <c r="H2" s="4" t="str">
+        <f>B4</f>
+        <v>CheeseBread</v>
       </c>
       <c r="J2" s="3" t="str">
         <f>reference!B2</f>
         <v>Apple</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>9</v>
+      <c r="K2" s="4" t="str">
+        <f>B5</f>
+        <v>Beer</v>
       </c>
       <c r="M2" s="3" t="str">
         <f>reference!B2</f>
         <v>Apple</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>10</v>
+      <c r="N2" s="4" t="str">
+        <f>B6</f>
+        <v>Cheese</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
@@ -572,35 +579,38 @@
         <v>Beer</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D3" s="3" t="str">
         <f>reference!B3</f>
         <v>Beer</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G3" s="3" t="str">
         <f>reference!B3</f>
         <v>Beer</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>8</v>
+      <c r="H3" s="4" t="str">
+        <f>E4</f>
+        <v>Apple</v>
       </c>
       <c r="J3" s="3" t="str">
         <f>reference!B3</f>
         <v>Beer</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>9</v>
+      <c r="K3" s="4" t="str">
+        <f>E5</f>
+        <v>Apple</v>
       </c>
       <c r="M3" s="3" t="str">
         <f>reference!B3</f>
         <v>Beer</v>
       </c>
-      <c r="N3" s="4" t="s">
-        <v>10</v>
+      <c r="N3" s="4" t="str">
+        <f>E6</f>
+        <v>Apple</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
@@ -609,7 +619,7 @@
         <v>Bread</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="str">
         <f>reference!B4</f>
@@ -623,21 +633,23 @@
         <v>Bread</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J4" s="3" t="str">
         <f>reference!B4</f>
         <v>Bread</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>9</v>
+      <c r="K4" s="4" t="str">
+        <f>H5</f>
+        <v>Bread</v>
       </c>
       <c r="M4" s="3" t="str">
         <f>reference!B4</f>
         <v>Bread</v>
       </c>
-      <c r="N4" s="4" t="s">
-        <v>10</v>
+      <c r="N4" s="4" t="str">
+        <f>H6</f>
+        <v>Bread</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
@@ -667,14 +679,15 @@
         <v>Cheese</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M5" s="3" t="str">
         <f>reference!B5</f>
         <v>Cheese</v>
       </c>
-      <c r="N5" s="4" t="s">
-        <v>10</v>
+      <c r="N5" s="4" t="str">
+        <f>K6</f>
+        <v>CheeseBread</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.4">
@@ -683,7 +696,7 @@
         <v>CheeseBread</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="str">
         <f>reference!B6</f>
@@ -711,7 +724,7 @@
         <v>CheeseBread</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/DXLibProject_Start/Resource/CSV/ItemRecipe.xlsx
+++ b/DXLibProject_Start/Resource/CSV/ItemRecipe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Resource\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2ED9B8-7778-471E-878D-18494FBE5D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D65EE0FF-DB76-4C0B-8B64-711840BFEFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{218ED3FD-F1A3-4748-B667-4E69C2DB56C8}"/>
+    <workbookView xWindow="7080" yWindow="-12840" windowWidth="21600" windowHeight="11295" xr2:uid="{218ED3FD-F1A3-4748-B667-4E69C2DB56C8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,55 +38,41 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Invalid</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>Apple</t>
+    <t>Honey</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Beer</t>
+    <t>Jam</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Bread</t>
+    <t>Pepper</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Cheese</t>
+    <t>Whiskey</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>CheeseBread</t>
+    <t>MolotovCocktail</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Beer</t>
-  </si>
-  <si>
-    <t>Bread</t>
-  </si>
-  <si>
-    <t>CheeseBread</t>
-  </si>
-  <si>
-    <t>Cheese</t>
-  </si>
-  <si>
-    <t>Invalid</t>
+    <t>HealBottle</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -106,6 +92,14 @@
       <sz val="11"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -165,7 +159,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -178,7 +172,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -495,236 +492,350 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FD5539C-A02E-4A9C-A317-3FB1655D1A37}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.625" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="15.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="str">
         <f>reference!B2</f>
-        <v>Apple</v>
+        <v>Honey</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="str">
         <f>reference!B3</f>
-        <v>Beer</v>
+        <v>Jam</v>
       </c>
       <c r="G1" s="1"/>
       <c r="H1" s="2" t="str">
         <f>reference!B4</f>
-        <v>Bread</v>
+        <v>Pepper</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="2" t="str">
         <f>reference!B5</f>
-        <v>Cheese</v>
+        <v>Whiskey</v>
       </c>
       <c r="M1" s="1"/>
       <c r="N1" s="2" t="str">
         <f>reference!B6</f>
-        <v>CheeseBread</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+        <v>HealBottle</v>
+      </c>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="2" t="str">
+        <f>reference!B5</f>
+        <v>Whiskey</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="str">
         <f>reference!B2</f>
-        <v>Apple</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>Honey</v>
+      </c>
+      <c r="B2" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
       <c r="D2" s="3" t="str">
         <f>reference!B2</f>
-        <v>Apple</v>
+        <v>Honey</v>
       </c>
       <c r="E2" s="4" t="str">
         <f>B3</f>
-        <v>Invalid</v>
+        <v>HealBottle</v>
       </c>
       <c r="G2" s="3" t="str">
         <f>reference!B2</f>
-        <v>Apple</v>
+        <v>Honey</v>
       </c>
       <c r="H2" s="4" t="str">
         <f>B4</f>
-        <v>CheeseBread</v>
+        <v>Invalid</v>
       </c>
       <c r="J2" s="3" t="str">
         <f>reference!B2</f>
-        <v>Apple</v>
+        <v>Honey</v>
       </c>
       <c r="K2" s="4" t="str">
         <f>B5</f>
-        <v>Beer</v>
+        <v>Invalid</v>
       </c>
       <c r="M2" s="3" t="str">
         <f>reference!B2</f>
-        <v>Apple</v>
+        <v>Honey</v>
       </c>
       <c r="N2" s="4" t="str">
         <f>B6</f>
-        <v>Cheese</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+        <v>Invalid</v>
+      </c>
+      <c r="P2" s="3" t="str">
+        <f>reference!B2</f>
+        <v>Honey</v>
+      </c>
+      <c r="Q2" s="4" t="str">
+        <f>B7</f>
+        <v>Invalid</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="str">
         <f>reference!B3</f>
-        <v>Beer</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>Jam</v>
+      </c>
+      <c r="B3" s="4" t="str">
+        <f>reference!B6</f>
+        <v>HealBottle</v>
       </c>
       <c r="D3" s="3" t="str">
         <f>reference!B3</f>
-        <v>Beer</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>11</v>
+        <v>Jam</v>
+      </c>
+      <c r="E3" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
       <c r="G3" s="3" t="str">
         <f>reference!B3</f>
-        <v>Beer</v>
+        <v>Jam</v>
       </c>
       <c r="H3" s="4" t="str">
         <f>E4</f>
-        <v>Apple</v>
+        <v>Invalid</v>
       </c>
       <c r="J3" s="3" t="str">
         <f>reference!B3</f>
-        <v>Beer</v>
+        <v>Jam</v>
       </c>
       <c r="K3" s="4" t="str">
         <f>E5</f>
-        <v>Apple</v>
+        <v>Invalid</v>
       </c>
       <c r="M3" s="3" t="str">
         <f>reference!B3</f>
-        <v>Beer</v>
+        <v>Jam</v>
       </c>
       <c r="N3" s="4" t="str">
         <f>E6</f>
-        <v>Apple</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+        <v>Invalid</v>
+      </c>
+      <c r="P3" s="3" t="str">
+        <f>reference!B3</f>
+        <v>Jam</v>
+      </c>
+      <c r="Q3" s="4" t="str">
+        <f>E7</f>
+        <v>Invalid</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="str">
         <f>reference!B4</f>
-        <v>Bread</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>Pepper</v>
+      </c>
+      <c r="B4" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
       <c r="D4" s="3" t="str">
         <f>reference!B4</f>
-        <v>Bread</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>1</v>
+        <v>Pepper</v>
+      </c>
+      <c r="E4" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
       <c r="G4" s="3" t="str">
         <f>reference!B4</f>
-        <v>Bread</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>11</v>
+        <v>Pepper</v>
+      </c>
+      <c r="H4" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
       <c r="J4" s="3" t="str">
         <f>reference!B4</f>
-        <v>Bread</v>
+        <v>Pepper</v>
       </c>
       <c r="K4" s="4" t="str">
         <f>H5</f>
-        <v>Bread</v>
+        <v>MolotovCocktail</v>
       </c>
       <c r="M4" s="3" t="str">
         <f>reference!B4</f>
-        <v>Bread</v>
+        <v>Pepper</v>
       </c>
       <c r="N4" s="4" t="str">
         <f>H6</f>
-        <v>Bread</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+        <v>Invalid</v>
+      </c>
+      <c r="P4" s="3" t="str">
+        <f>reference!B4</f>
+        <v>Pepper</v>
+      </c>
+      <c r="Q4" s="4" t="str">
+        <f>H7</f>
+        <v>Invalid</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="str">
         <f>reference!B5</f>
-        <v>Cheese</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>7</v>
+        <v>Whiskey</v>
+      </c>
+      <c r="B5" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
       <c r="D5" s="3" t="str">
         <f>reference!B5</f>
-        <v>Cheese</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>1</v>
+        <v>Whiskey</v>
+      </c>
+      <c r="E5" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
       <c r="G5" s="3" t="str">
         <f>reference!B5</f>
-        <v>Cheese</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>8</v>
+        <v>Whiskey</v>
+      </c>
+      <c r="H5" s="4" t="str">
+        <f>reference!B7</f>
+        <v>MolotovCocktail</v>
       </c>
       <c r="J5" s="3" t="str">
         <f>reference!B5</f>
-        <v>Cheese</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>11</v>
+        <v>Whiskey</v>
+      </c>
+      <c r="K5" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
       <c r="M5" s="3" t="str">
         <f>reference!B5</f>
-        <v>Cheese</v>
+        <v>Whiskey</v>
       </c>
       <c r="N5" s="4" t="str">
         <f>K6</f>
-        <v>CheeseBread</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+        <v>Invalid</v>
+      </c>
+      <c r="P5" s="3" t="str">
+        <f>reference!B5</f>
+        <v>Whiskey</v>
+      </c>
+      <c r="Q5" s="4" t="str">
+        <f>K7</f>
+        <v>Invalid</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="str">
         <f>reference!B6</f>
-        <v>CheeseBread</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>HealBottle</v>
+      </c>
+      <c r="B6" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
       <c r="D6" s="3" t="str">
         <f>reference!B6</f>
-        <v>CheeseBread</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>1</v>
+        <v>HealBottle</v>
+      </c>
+      <c r="E6" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
       <c r="G6" s="3" t="str">
         <f>reference!B6</f>
-        <v>CheeseBread</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>8</v>
+        <v>HealBottle</v>
+      </c>
+      <c r="H6" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
       <c r="J6" s="3" t="str">
         <f>reference!B6</f>
-        <v>CheeseBread</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>9</v>
+        <v>HealBottle</v>
+      </c>
+      <c r="K6" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
       <c r="M6" s="3" t="str">
         <f>reference!B6</f>
-        <v>CheeseBread</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>11</v>
+        <v>HealBottle</v>
+      </c>
+      <c r="N6" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
+      </c>
+      <c r="P6" s="3" t="str">
+        <f>reference!B6</f>
+        <v>HealBottle</v>
+      </c>
+      <c r="Q6" s="4" t="str">
+        <f>N7</f>
+        <v>Invalid</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="str">
+        <f>reference!B7</f>
+        <v>MolotovCocktail</v>
+      </c>
+      <c r="B7" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
+      </c>
+      <c r="D7" s="3" t="str">
+        <f>reference!B7</f>
+        <v>MolotovCocktail</v>
+      </c>
+      <c r="E7" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
+      </c>
+      <c r="G7" s="3" t="str">
+        <f>reference!B7</f>
+        <v>MolotovCocktail</v>
+      </c>
+      <c r="H7" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
+      </c>
+      <c r="J7" s="3" t="str">
+        <f>reference!B7</f>
+        <v>MolotovCocktail</v>
+      </c>
+      <c r="K7" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
+      </c>
+      <c r="M7" s="3" t="str">
+        <f>reference!B7</f>
+        <v>MolotovCocktail</v>
+      </c>
+      <c r="N7" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
+      </c>
+      <c r="P7" s="3" t="str">
+        <f>reference!B7</f>
+        <v>MolotovCocktail</v>
+      </c>
+      <c r="Q7" s="4" t="str">
+        <f>reference!B1</f>
+        <v>Invalid</v>
       </c>
     </row>
   </sheetData>
@@ -738,7 +849,7 @@
           <x14:formula1>
             <xm:f>reference!$B:$B</xm:f>
           </x14:formula1>
-          <xm:sqref>K1 B1 A2:B6 G2:H6 N1 E1 D2:E6 H1 J2:K6 M2:N6</xm:sqref>
+          <xm:sqref>K1 B1 H1 G2:G7 A2:A7 E1 D2:D7 J2:J7 N1 M2:M7 Q1 P2:P7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -748,10 +859,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70688D63-630F-42E1-933D-89BA8B150096}">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
@@ -767,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.4">
@@ -775,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.4">
@@ -783,7 +895,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.4">
@@ -791,7 +903,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.4">
@@ -802,8 +914,17 @@
         <v>6</v>
       </c>
     </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>